--- a/游戏设计王/老虎机数学专题-中列扩展百搭.xlsx
+++ b/游戏设计王/老虎机数学专题-中列扩展百搭.xlsx
@@ -3,14 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\slotRtp\游戏设计王\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="中列扩展 走线+三线RTP" sheetId="7" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4394" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4394" uniqueCount="132">
   <si>
     <t>中列扩展百搭 Middle Row Expanding Wild（原文数据版）</t>
   </si>
@@ -381,12 +386,6 @@
   </si>
   <si>
     <t>J</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
   <si>
     <t>【走线表】</t>
@@ -1230,7 +1229,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1272,31 +1271,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1322,7 +1296,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1412,8 +1385,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5943600" y="6197600"/>
-          <a:ext cx="5461000" cy="2654300"/>
+          <a:off x="6480810" y="6184900"/>
+          <a:ext cx="5918200" cy="2647950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1448,8 +1421,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5943600" y="8953500"/>
-          <a:ext cx="5321300" cy="4114800"/>
+          <a:off x="6480810" y="8934450"/>
+          <a:ext cx="5778500" cy="4146550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1484,8 +1457,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5943600" y="13169900"/>
-          <a:ext cx="5461000" cy="2743200"/>
+          <a:off x="6480810" y="13182600"/>
+          <a:ext cx="5918200" cy="2546350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1520,8 +1493,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5943600" y="16014700"/>
-          <a:ext cx="5461000" cy="1689100"/>
+          <a:off x="6480810" y="15855950"/>
+          <a:ext cx="5918200" cy="1790700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1819,9 +1792,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M88"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="84.6363636363636" style="18" customWidth="1"/>
+    <col min="1" max="1" width="84.6333333333333" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:10">
@@ -1856,7 +1829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:10">
+    <row r="2" ht="14" customHeight="1" spans="1:10">
       <c r="A2" s="21" t="s">
         <v>2</v>
       </c>
@@ -1888,7 +1861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:10">
+    <row r="3" ht="14" customHeight="1" spans="1:10">
       <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
@@ -1920,7 +1893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:10">
+    <row r="4" ht="14" customHeight="1" spans="1:10">
       <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
@@ -1952,7 +1925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:10">
+    <row r="5" ht="14" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
         <v>4</v>
       </c>
@@ -1984,7 +1957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:10">
+    <row r="6" ht="14" customHeight="1" spans="1:10">
       <c r="A6" s="21" t="s">
         <v>5</v>
       </c>
@@ -2016,7 +1989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:10">
+    <row r="7" ht="14" customHeight="1" spans="1:10">
       <c r="A7" s="21" t="s">
         <v>6</v>
       </c>
@@ -2048,7 +2021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:10">
+    <row r="8" ht="14" customHeight="1" spans="1:10">
       <c r="A8" s="21" t="s">
         <v>7</v>
       </c>
@@ -2080,7 +2053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:10">
+    <row r="9" ht="14" customHeight="1" spans="1:10">
       <c r="A9" s="21" t="s">
         <v>8</v>
       </c>
@@ -2112,7 +2085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:10">
+    <row r="10" ht="14" customHeight="1" spans="1:10">
       <c r="A10" s="21" t="s">
         <v>9</v>
       </c>
@@ -2144,7 +2117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:10">
+    <row r="11" ht="14" customHeight="1" spans="1:10">
       <c r="A11" s="21" t="s">
         <v>10</v>
       </c>
@@ -2176,7 +2149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:10">
+    <row r="12" ht="14" customHeight="1" spans="1:10">
       <c r="A12" s="21" t="s">
         <v>11</v>
       </c>
@@ -2208,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:10">
+    <row r="13" ht="14" customHeight="1" spans="1:10">
       <c r="A13" s="21" t="s">
         <v>12</v>
       </c>
@@ -2240,7 +2213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:10">
+    <row r="14" ht="14" customHeight="1" spans="1:10">
       <c r="A14" s="21" t="s">
         <v>13</v>
       </c>
@@ -2272,7 +2245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:10">
+    <row r="15" ht="14" customHeight="1" spans="1:10">
       <c r="A15" s="21" t="s">
         <v>14</v>
       </c>
@@ -2304,7 +2277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:10">
+    <row r="16" ht="14" customHeight="1" spans="1:10">
       <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
@@ -2336,7 +2309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:10">
+    <row r="17" ht="14" customHeight="1" spans="1:10">
       <c r="A17" s="21" t="s">
         <v>16</v>
       </c>
@@ -2368,7 +2341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:10">
+    <row r="18" ht="14" customHeight="1" spans="1:10">
       <c r="A18" s="21" t="s">
         <v>17</v>
       </c>
@@ -2400,7 +2373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:10">
+    <row r="19" ht="14" customHeight="1" spans="1:10">
       <c r="A19" s="21" t="s">
         <v>1</v>
       </c>
@@ -2432,7 +2405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:10">
+    <row r="20" ht="14" customHeight="1" spans="1:10">
       <c r="A20" s="21" t="s">
         <v>18</v>
       </c>
@@ -2464,7 +2437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:10">
+    <row r="21" ht="14" customHeight="1" spans="1:10">
       <c r="A21" s="21" t="s">
         <v>19</v>
       </c>
@@ -2496,7 +2469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:10">
+    <row r="22" ht="14" customHeight="1" spans="1:10">
       <c r="A22" s="21" t="s">
         <v>1</v>
       </c>
@@ -2528,7 +2501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:10">
+    <row r="23" ht="14" customHeight="1" spans="1:10">
       <c r="A23" s="23" t="s">
         <v>20</v>
       </c>
@@ -2625,1940 +2598,1940 @@
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:10">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="37" t="s">
+      <c r="B26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="37" t="s">
+      <c r="A27" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:10">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="37" t="s">
+      <c r="B28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:10">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="37" t="s">
+      <c r="B29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:10">
-      <c r="A30" s="39" t="s">
+      <c r="A30" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="37" t="s">
+      <c r="B30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:10">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="37" t="s">
+      <c r="B31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="37" t="s">
+      <c r="A32" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:10">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="37" t="s">
+      <c r="B33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:10">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="37" t="s">
+      <c r="B34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:10">
-      <c r="A35" s="42" t="s">
+      <c r="A35" s="31" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:10">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="37" t="s">
+      <c r="B36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:10">
-      <c r="A37" s="40" t="s">
+      <c r="A37" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="37" t="s">
+      <c r="B37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="37" t="s">
+      <c r="A38" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:10">
-      <c r="A39" s="41" t="s">
+      <c r="A39" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="37" t="s">
+      <c r="B39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:10">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="37" t="s">
+      <c r="B40" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:10">
-      <c r="A41" s="41" t="s">
+      <c r="A41" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="37" t="s">
+      <c r="B41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:10">
-      <c r="A42" s="41" t="s">
+      <c r="A42" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="37" t="s">
+      <c r="B42" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:10">
-      <c r="A43" s="41" t="s">
+      <c r="A43" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="37" t="s">
+      <c r="B43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:10">
-      <c r="A44" s="41" t="s">
+      <c r="A44" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="37" t="s">
+      <c r="B44" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="37" t="s">
+      <c r="B45" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:10">
-      <c r="A46" s="41" t="s">
+      <c r="A46" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="37" t="s">
+      <c r="B46" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:10">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="37" t="s">
+      <c r="B47" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="37" t="s">
+      <c r="A48" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:10">
-      <c r="A49" s="41" t="s">
+      <c r="A49" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="37" t="s">
+      <c r="B49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:10">
-      <c r="A50" s="40" t="s">
+      <c r="A50" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="37" t="s">
+      <c r="B50" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="37" t="s">
+      <c r="A51" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:10">
-      <c r="A52" s="42" t="s">
+      <c r="A52" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="37" t="s">
+      <c r="B52" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:10">
-      <c r="A53" s="42" t="s">
+      <c r="A53" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="37" t="s">
+      <c r="B53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:10">
-      <c r="A54" s="41" t="s">
+      <c r="A54" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="37" t="s">
+      <c r="B54" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:10">
-      <c r="A55" s="41" t="s">
+      <c r="A55" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I55" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="37" t="s">
+      <c r="B55" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:10">
-      <c r="A56" s="41" t="s">
+      <c r="A56" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J56" s="37" t="s">
+      <c r="B56" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I56" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J56" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:10">
-      <c r="A57" s="41" t="s">
+      <c r="A57" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="37" t="s">
+      <c r="B57" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:10">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="B58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="37" t="s">
+      <c r="B58" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:10">
-      <c r="A59" s="41" t="s">
+      <c r="A59" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I59" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59" s="37" t="s">
+      <c r="B59" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:10">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="B60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="37" t="s">
+      <c r="B60" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" spans="1:10">
-      <c r="A61" s="43" t="s">
+      <c r="A61" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="44" t="s">
+      <c r="B61" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" ht="14.5" spans="1:10">
-      <c r="A62" s="45" t="s">
+      <c r="C61" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:10">
+      <c r="A62" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="B62" s="46" t="s">
+      <c r="B62" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="C62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" ht="14.5" spans="1:10">
-      <c r="A63" s="45" t="s">
+      <c r="C62" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:10">
+      <c r="A63" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B63" s="46" t="s">
+      <c r="B63" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="C63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="37" t="s">
+      <c r="C63" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I64" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J64" s="37" t="s">
+      <c r="A64" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H64" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:10">
-      <c r="A65" s="40" t="s">
+      <c r="A65" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="B65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="37" t="s">
+      <c r="B65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I66" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J66" s="37" t="s">
+      <c r="A66" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:10">
-      <c r="A67" s="41" t="s">
+      <c r="A67" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="B67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I67" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J67" s="37" t="s">
+      <c r="B67" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:10">
-      <c r="A68" s="41" t="s">
+      <c r="A68" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="B68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I68" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" ht="33" spans="1:10">
-      <c r="A69" s="41" t="s">
+      <c r="B68" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:10">
+      <c r="A69" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J69" s="37" t="s">
+      <c r="B69" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:10">
-      <c r="A70" s="42" t="s">
+      <c r="A70" s="31" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:10">
-      <c r="A71" s="41" t="s">
+      <c r="A71" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71" s="37" t="s">
+      <c r="B71" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I71" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:10">
-      <c r="A72" s="42" t="s">
+      <c r="A72" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J72" s="37" t="s">
+      <c r="B72" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H72" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I72" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:10">
-      <c r="A73" s="41" t="s">
+      <c r="A73" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J73" s="37" t="s">
+      <c r="B73" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H73" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I73" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:10">
-      <c r="A74" s="40" t="s">
+      <c r="A74" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J74" s="37" t="s">
+      <c r="B74" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H74" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I74" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I75" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J75" s="37" t="s">
+      <c r="A75" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I75" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" spans="1:10">
-      <c r="A76" s="43" t="s">
+      <c r="A76" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="B76" s="44" t="s">
+      <c r="B76" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I76" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J76" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" ht="14.5" spans="1:10">
-      <c r="A77" s="45" t="s">
+      <c r="C76" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D76" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H76" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I76" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J76" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:10">
+      <c r="A77" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="B77" s="46" t="s">
+      <c r="B77" s="35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="78" ht="14.5" spans="1:10">
-      <c r="A78" s="45" t="s">
+    <row r="78" ht="16.5" spans="1:10">
+      <c r="A78" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B78" s="46" t="s">
+      <c r="B78" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I78" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J78" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" ht="14.5" spans="1:10">
-      <c r="A79" s="45" t="s">
+      <c r="C78" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E78" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G78" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H78" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I78" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J78" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:10">
+      <c r="A79" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B79" s="46" t="s">
+      <c r="B79" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I79" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J79" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" ht="14.5" spans="1:10">
-      <c r="A80" s="45" t="s">
+      <c r="C79" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E79" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G79" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H79" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I79" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J79" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:10">
+      <c r="A80" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="B80" s="46" t="s">
+      <c r="B80" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I80" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J80" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" ht="14.5" spans="1:10">
-      <c r="A81" s="45" t="s">
+      <c r="C80" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G80" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H80" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I80" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J80" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:10">
+      <c r="A81" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B81" s="46" t="s">
+      <c r="B81" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I81" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J81" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" ht="14.5" spans="1:10">
-      <c r="A82" s="45" t="s">
+      <c r="C81" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E81" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G81" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H81" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I81" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J81" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" spans="1:10">
+      <c r="A82" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="46" t="s">
+      <c r="B82" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="C82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I82" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J82" s="37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" ht="14.5" spans="1:10">
-      <c r="A83" s="45" t="s">
+      <c r="C82" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E82" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G82" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H82" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I82" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J82" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" ht="16.5" spans="1:10">
+      <c r="A83" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="B83" s="46" t="s">
+      <c r="B83" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I83" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J83" s="37" t="s">
+      <c r="C83" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E83" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G83" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H83" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I83" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J83" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I84" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J84" s="37" t="s">
+      <c r="A84" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J84" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I85" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J85" s="37" t="s">
+      <c r="A85" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J85" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I86" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J86" s="37" t="s">
+      <c r="A86" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J86" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I87" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J87" s="37" t="s">
+      <c r="A87" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J87" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="I88" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J88" s="37" t="s">
+      <c r="A88" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J88" s="26" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4599,14 +4572,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T205"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="39.4545454545455" customWidth="1"/>
-    <col min="2" max="2" width="14.8181818181818" customWidth="1"/>
+    <col min="1" max="1" width="39.4583333333333" customWidth="1"/>
+    <col min="2" max="2" width="14.8166666666667" customWidth="1"/>
     <col min="3" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:20">
+    <row r="1" ht="14" customHeight="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
@@ -4792,7 +4765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:20">
+    <row r="4" ht="14" customHeight="1" spans="1:20">
       <c r="A4" s="5" t="s">
         <v>82</v>
       </c>
@@ -5044,7 +5017,7 @@
       <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="4">
         <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -5106,19 +5079,19 @@
       <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="4">
         <v>9</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="4">
         <v>10</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="4">
         <v>10</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="4">
         <v>10</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="4">
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -5168,19 +5141,19 @@
       <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="4">
         <v>9</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="4">
         <v>9</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="4">
         <v>9</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="4">
         <v>9</v>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="4">
         <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -5242,7 +5215,7 @@
       <c r="E11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="4">
         <v>9</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -5416,7 +5389,7 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="4">
         <v>10</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -5478,19 +5451,19 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="4">
         <v>10</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="4">
         <v>10</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="4">
         <v>10</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="4">
         <v>10</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="4">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -5543,16 +5516,16 @@
       <c r="B16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="4">
         <v>9</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="4">
         <v>9</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="4">
         <v>9</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="4">
         <v>9</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -5664,7 +5637,7 @@
       <c r="A18" s="4">
         <v>14</v>
       </c>
-      <c r="B18" s="47">
+      <c r="B18" s="4">
         <v>10</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -5726,7 +5699,7 @@
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="47">
+      <c r="B19" s="4">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -5788,19 +5761,19 @@
       <c r="A20" s="4">
         <v>16</v>
       </c>
-      <c r="B20" s="47">
+      <c r="B20" s="4">
         <v>9</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="4">
         <v>10</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="4">
         <v>10</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E20" s="4">
         <v>10</v>
       </c>
-      <c r="F20" s="47">
+      <c r="F20" s="4">
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
@@ -5853,16 +5826,16 @@
       <c r="B21" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="4">
         <v>9</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="4">
         <v>9</v>
       </c>
-      <c r="E21" s="47">
+      <c r="E21" s="4">
         <v>9</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="4">
         <v>9</v>
       </c>
       <c r="G21" s="2" t="s">
@@ -5912,7 +5885,7 @@
       <c r="A22" s="4">
         <v>18</v>
       </c>
-      <c r="B22" s="47">
+      <c r="B22" s="4">
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -5974,19 +5947,19 @@
       <c r="A23" s="4">
         <v>19</v>
       </c>
-      <c r="B23" s="47">
+      <c r="B23" s="4">
         <v>9</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="47">
+      <c r="D23" s="4">
         <v>10</v>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="4">
         <v>10</v>
       </c>
-      <c r="F23" s="47">
+      <c r="F23" s="4">
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
@@ -6036,19 +6009,19 @@
       <c r="A24" s="4">
         <v>20</v>
       </c>
-      <c r="B24" s="47">
+      <c r="B24" s="4">
         <v>9</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="4">
         <v>9</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="4">
         <v>9</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="4">
         <v>9</v>
       </c>
-      <c r="F24" s="47">
+      <c r="F24" s="4">
         <v>9</v>
       </c>
       <c r="G24" s="2" t="s">
@@ -6156,9 +6129,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:20">
+    <row r="26" ht="14" customHeight="1" spans="1:20">
       <c r="A26" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1</v>
@@ -6220,7 +6193,7 @@
     </row>
     <row r="27" ht="16.5" spans="1:20">
       <c r="A27" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>1</v>
@@ -6342,24 +6315,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:20">
+    <row r="29" ht="14" customHeight="1" spans="1:20">
       <c r="A29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>1</v>
@@ -6406,7 +6379,7 @@
     </row>
     <row r="30" ht="16.5" spans="1:20">
       <c r="A30" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B30" s="8">
         <v>1</v>
@@ -6468,7 +6441,7 @@
     </row>
     <row r="31" ht="16.5" spans="1:20">
       <c r="A31" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B31" s="8">
         <v>3</v>
@@ -6530,7 +6503,7 @@
     </row>
     <row r="32" ht="16.5" spans="1:20">
       <c r="A32" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B32" s="8">
         <v>3</v>
@@ -6652,9 +6625,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:20">
+    <row r="34" ht="14" customHeight="1" spans="1:20">
       <c r="A34" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>1</v>
@@ -6716,7 +6689,7 @@
     </row>
     <row r="35" ht="16.5" spans="1:20">
       <c r="A35" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1</v>
@@ -6838,7 +6811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:20">
+    <row r="37" ht="14" customHeight="1" spans="1:20">
       <c r="A37" s="5" t="s">
         <v>83</v>
       </c>
@@ -6902,7 +6875,7 @@
     </row>
     <row r="38" ht="16.5" spans="1:20">
       <c r="A38" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B38" s="4">
         <v>20</v>
@@ -7211,7 +7184,7 @@
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:20">
-      <c r="A43" s="47">
+      <c r="A43" s="4">
         <v>10</v>
       </c>
       <c r="B43" s="8">
@@ -7273,7 +7246,7 @@
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:20">
-      <c r="A44" s="47">
+      <c r="A44" s="4">
         <v>9</v>
       </c>
       <c r="B44" s="8">
@@ -7336,7 +7309,7 @@
     </row>
     <row r="45" ht="16.5" spans="1:20">
       <c r="A45" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B45" s="4">
         <f>B40+B39</f>
@@ -7399,7 +7372,7 @@
     </row>
     <row r="46" ht="16.5" spans="1:20">
       <c r="A46" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B46" s="4">
         <f>B41+B39</f>
@@ -7462,7 +7435,7 @@
     </row>
     <row r="47" ht="16.5" spans="1:20">
       <c r="A47" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B47" s="4">
         <f>B42+B39</f>
@@ -7525,7 +7498,7 @@
     </row>
     <row r="48" ht="16.5" spans="1:20">
       <c r="A48" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B48" s="4">
         <f>B43+B39</f>
@@ -7588,7 +7561,7 @@
     </row>
     <row r="49" ht="16.5" spans="1:20">
       <c r="A49" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B49" s="4">
         <f>B44+B39</f>
@@ -7651,7 +7624,7 @@
     </row>
     <row r="50" ht="16.5" spans="1:20">
       <c r="A50" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B50" s="4">
         <f>20-B45</f>
@@ -7714,7 +7687,7 @@
     </row>
     <row r="51" ht="16.5" spans="1:20">
       <c r="A51" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B51" s="4">
         <f>20-B46</f>
@@ -7777,7 +7750,7 @@
     </row>
     <row r="52" ht="16.5" spans="1:20">
       <c r="A52" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B52" s="4">
         <f>20-B47</f>
@@ -7840,7 +7813,7 @@
     </row>
     <row r="53" ht="16.5" spans="1:20">
       <c r="A53" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B53" s="4">
         <f>20-B48</f>
@@ -7903,7 +7876,7 @@
     </row>
     <row r="54" ht="16.5" spans="1:20">
       <c r="A54" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B54" s="4">
         <f>20-B49</f>
@@ -8093,66 +8066,66 @@
         <v>84</v>
       </c>
       <c r="B57" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T57" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K57" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="S57" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="T57" s="12" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:20">
       <c r="A58" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B58" s="4">
         <v>20</v>
@@ -8461,7 +8434,7 @@
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:20">
-      <c r="A63" s="47">
+      <c r="A63" s="4">
         <v>10</v>
       </c>
       <c r="B63" s="8">
@@ -8523,7 +8496,7 @@
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:20">
-      <c r="A64" s="47">
+      <c r="A64" s="4">
         <v>9</v>
       </c>
       <c r="B64" s="8">
@@ -8586,7 +8559,7 @@
     </row>
     <row r="65" ht="16.5" spans="1:20">
       <c r="A65" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B65" s="4">
         <f>B60+B59</f>
@@ -8651,7 +8624,7 @@
     </row>
     <row r="66" ht="16.5" spans="1:20">
       <c r="A66" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B66" s="4">
         <f>B61+B59</f>
@@ -8716,7 +8689,7 @@
     </row>
     <row r="67" ht="16.5" spans="1:20">
       <c r="A67" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B67" s="4">
         <f>B62+B59</f>
@@ -8781,7 +8754,7 @@
     </row>
     <row r="68" ht="16.5" spans="1:20">
       <c r="A68" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B68" s="4">
         <f>B63+B59</f>
@@ -8846,7 +8819,7 @@
     </row>
     <row r="69" ht="16.5" spans="1:20">
       <c r="A69" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B69" s="4">
         <f>B64+B59-1</f>
@@ -8911,7 +8884,7 @@
     </row>
     <row r="70" ht="16.5" spans="1:20">
       <c r="A70" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B70" s="4">
         <f>20-B65</f>
@@ -8976,7 +8949,7 @@
     </row>
     <row r="71" ht="16.5" spans="1:20">
       <c r="A71" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B71" s="4">
         <f>20-B66</f>
@@ -9041,7 +9014,7 @@
     </row>
     <row r="72" ht="16.5" spans="1:20">
       <c r="A72" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B72" s="4">
         <f>20-B67</f>
@@ -9106,7 +9079,7 @@
     </row>
     <row r="73" ht="16.5" spans="1:20">
       <c r="A73" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B73" s="4">
         <f>20-B68</f>
@@ -9171,7 +9144,7 @@
     </row>
     <row r="74" ht="16.5" spans="1:20">
       <c r="A74" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B74" s="4">
         <f>20-B69</f>
@@ -9363,66 +9336,66 @@
         <v>85</v>
       </c>
       <c r="B77" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K77" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T77" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K77" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="L77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="P77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="S77" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="T77" s="12" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:20">
       <c r="A78" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B78" s="4">
         <v>20</v>
@@ -9731,7 +9704,7 @@
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:20">
-      <c r="A83" s="47">
+      <c r="A83" s="4">
         <v>10</v>
       </c>
       <c r="B83" s="8">
@@ -9793,7 +9766,7 @@
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:20">
-      <c r="A84" s="47">
+      <c r="A84" s="4">
         <v>9</v>
       </c>
       <c r="B84" s="8">
@@ -9856,7 +9829,7 @@
     </row>
     <row r="85" ht="16.5" spans="1:20">
       <c r="A85" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B85" s="4">
         <f>B80+B79</f>
@@ -9921,7 +9894,7 @@
     </row>
     <row r="86" ht="16.5" spans="1:20">
       <c r="A86" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B86" s="4">
         <f>B81+B79</f>
@@ -9986,7 +9959,7 @@
     </row>
     <row r="87" ht="16.5" spans="1:20">
       <c r="A87" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B87" s="4">
         <f>B82+B79</f>
@@ -10051,7 +10024,7 @@
     </row>
     <row r="88" ht="16.5" spans="1:20">
       <c r="A88" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B88" s="4">
         <f>B83+B79</f>
@@ -10116,7 +10089,7 @@
     </row>
     <row r="89" ht="16.5" spans="1:20">
       <c r="A89" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B89" s="4">
         <f>B84+B79-1</f>
@@ -10181,7 +10154,7 @@
     </row>
     <row r="90" ht="16.5" spans="1:20">
       <c r="A90" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B90" s="4">
         <f>20-B85</f>
@@ -10246,7 +10219,7 @@
     </row>
     <row r="91" ht="16.5" spans="1:20">
       <c r="A91" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B91" s="4">
         <f>20-B86</f>
@@ -10311,7 +10284,7 @@
     </row>
     <row r="92" ht="16.5" spans="1:20">
       <c r="A92" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B92" s="4">
         <f>20-B87</f>
@@ -10376,7 +10349,7 @@
     </row>
     <row r="93" ht="16.5" spans="1:20">
       <c r="A93" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B93" s="4">
         <f>20-B88</f>
@@ -10441,7 +10414,7 @@
     </row>
     <row r="94" ht="16.5" spans="1:20">
       <c r="A94" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B94" s="4">
         <f>20-B89</f>
@@ -10633,66 +10606,66 @@
         <v>86</v>
       </c>
       <c r="B97" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K97" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T97" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K97" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="L97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="P97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="S97" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="T97" s="12" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:20">
       <c r="A98" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B98" s="4">
         <v>20</v>
@@ -11001,7 +10974,7 @@
       </c>
     </row>
     <row r="103" ht="16.5" spans="1:20">
-      <c r="A103" s="47">
+      <c r="A103" s="4">
         <v>10</v>
       </c>
       <c r="B103" s="8">
@@ -11063,7 +11036,7 @@
       </c>
     </row>
     <row r="104" ht="16.5" spans="1:20">
-      <c r="A104" s="47">
+      <c r="A104" s="4">
         <v>9</v>
       </c>
       <c r="B104" s="8">
@@ -11126,7 +11099,7 @@
     </row>
     <row r="105" ht="16.5" spans="1:20">
       <c r="A105" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B105" s="4">
         <f>B100+B99</f>
@@ -11191,7 +11164,7 @@
     </row>
     <row r="106" ht="16.5" spans="1:20">
       <c r="A106" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B106" s="4">
         <f>B101+B99</f>
@@ -11256,7 +11229,7 @@
     </row>
     <row r="107" ht="16.5" spans="1:20">
       <c r="A107" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B107" s="4">
         <f>B102+B99</f>
@@ -11321,7 +11294,7 @@
     </row>
     <row r="108" ht="16.5" spans="1:20">
       <c r="A108" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B108" s="4">
         <f>B103+B99</f>
@@ -11386,7 +11359,7 @@
     </row>
     <row r="109" ht="16.5" spans="1:20">
       <c r="A109" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B109" s="4">
         <f>B104+B99-1</f>
@@ -11451,7 +11424,7 @@
     </row>
     <row r="110" ht="16.5" spans="1:20">
       <c r="A110" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B110" s="4">
         <f>20-B105</f>
@@ -11516,7 +11489,7 @@
     </row>
     <row r="111" ht="16.5" spans="1:20">
       <c r="A111" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B111" s="4">
         <f>20-B106</f>
@@ -11581,7 +11554,7 @@
     </row>
     <row r="112" ht="16.5" spans="1:20">
       <c r="A112" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B112" s="4">
         <f>20-B107</f>
@@ -11646,7 +11619,7 @@
     </row>
     <row r="113" ht="16.5" spans="1:20">
       <c r="A113" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B113" s="4">
         <f>20-B108</f>
@@ -11711,7 +11684,7 @@
     </row>
     <row r="114" ht="16.5" spans="1:20">
       <c r="A114" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B114" s="4">
         <f>20-B109</f>
@@ -11903,66 +11876,66 @@
         <v>87</v>
       </c>
       <c r="B117" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K117" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T117" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K117" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="L117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="P117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="S117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="T117" s="12" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:20">
       <c r="A118" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B118" s="4">
         <v>20</v>
@@ -12271,7 +12244,7 @@
       </c>
     </row>
     <row r="123" ht="16.5" spans="1:20">
-      <c r="A123" s="47">
+      <c r="A123" s="4">
         <v>10</v>
       </c>
       <c r="B123" s="8">
@@ -12333,7 +12306,7 @@
       </c>
     </row>
     <row r="124" ht="16.5" spans="1:20">
-      <c r="A124" s="47">
+      <c r="A124" s="4">
         <v>9</v>
       </c>
       <c r="B124" s="8">
@@ -12396,7 +12369,7 @@
     </row>
     <row r="125" ht="16.5" spans="1:20">
       <c r="A125" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B125" s="4">
         <f>B120+B119</f>
@@ -12461,7 +12434,7 @@
     </row>
     <row r="126" ht="16.5" spans="1:20">
       <c r="A126" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B126" s="4">
         <f>B121+B119</f>
@@ -12526,7 +12499,7 @@
     </row>
     <row r="127" ht="16.5" spans="1:20">
       <c r="A127" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B127" s="4">
         <f>B122+B119</f>
@@ -12591,7 +12564,7 @@
     </row>
     <row r="128" ht="16.5" spans="1:20">
       <c r="A128" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B128" s="4">
         <f>B123+B119</f>
@@ -12656,7 +12629,7 @@
     </row>
     <row r="129" ht="16.5" spans="1:20">
       <c r="A129" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B129" s="4">
         <f>B124+B119-1</f>
@@ -12721,7 +12694,7 @@
     </row>
     <row r="130" ht="16.5" spans="1:20">
       <c r="A130" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B130" s="4">
         <f>20-B125</f>
@@ -12786,7 +12759,7 @@
     </row>
     <row r="131" ht="16.5" spans="1:20">
       <c r="A131" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B131" s="4">
         <f>20-B126</f>
@@ -12851,7 +12824,7 @@
     </row>
     <row r="132" ht="16.5" spans="1:20">
       <c r="A132" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B132" s="4">
         <f>20-B127</f>
@@ -12916,7 +12889,7 @@
     </row>
     <row r="133" ht="16.5" spans="1:20">
       <c r="A133" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B133" s="4">
         <f>20-B128</f>
@@ -12981,7 +12954,7 @@
     </row>
     <row r="134" ht="16.5" spans="1:20">
       <c r="A134" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B134" s="4">
         <f>20-B129</f>
@@ -13106,9 +13079,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="1:20">
+    <row r="136" ht="14" customHeight="1" spans="1:20">
       <c r="A136" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>1</v>
@@ -13170,7 +13143,7 @@
     </row>
     <row r="137" ht="16.5" spans="1:20">
       <c r="A137" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>1</v>
@@ -13292,9 +13265,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="1:20">
+    <row r="139" ht="14" customHeight="1" spans="1:20">
       <c r="A139" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>1</v>
@@ -13354,24 +13327,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="1:20">
+    <row r="140" ht="14" customHeight="1" spans="1:20">
       <c r="A140" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C140" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="D140" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="E140" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D140" s="5" t="s">
+      <c r="F140" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G140" s="6" t="s">
         <v>1</v>
@@ -13432,11 +13405,11 @@
         <v>0.000675</v>
       </c>
       <c r="E141" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F141" s="14">
         <f t="shared" ref="F141:F155" si="1">D141*E141</f>
-        <v>0.003375</v>
+        <v>0.0675</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>1</v>
@@ -13562,11 +13535,11 @@
         <v>0.0063</v>
       </c>
       <c r="E143" s="8">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F143" s="14">
         <f t="shared" si="1"/>
-        <v>0.63</v>
+        <v>0.0315</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>1</v>
@@ -13627,11 +13600,11 @@
         <v>0.0005859375</v>
       </c>
       <c r="E144" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F144" s="14">
         <f t="shared" si="1"/>
-        <v>0.0029296875</v>
+        <v>0.05859375</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>1</v>
@@ -13757,11 +13730,11 @@
         <v>0.00703125</v>
       </c>
       <c r="E146" s="8">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F146" s="14">
         <f t="shared" si="1"/>
-        <v>0.703125</v>
+        <v>0.03515625</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>1</v>
@@ -13822,11 +13795,11 @@
         <v>0.00189</v>
       </c>
       <c r="E147" s="8">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F147" s="14">
         <f t="shared" si="1"/>
-        <v>0.00945</v>
+        <v>0.14175</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>1</v>
@@ -13952,11 +13925,11 @@
         <v>0.0147</v>
       </c>
       <c r="E149" s="8">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F149" s="14">
         <f t="shared" si="1"/>
-        <v>1.1025</v>
+        <v>0.0735</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>1</v>
@@ -14002,7 +13975,7 @@
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:20">
-      <c r="A150" s="47">
+      <c r="A150" s="4">
         <v>10</v>
       </c>
       <c r="B150" s="4">
@@ -14017,11 +13990,11 @@
         <v>0.0016875</v>
       </c>
       <c r="E150" s="8">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F150" s="14">
         <f t="shared" si="1"/>
-        <v>0.0084375</v>
+        <v>0.1265625</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>1</v>
@@ -14067,7 +14040,7 @@
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:20">
-      <c r="A151" s="47">
+      <c r="A151" s="4">
         <v>10</v>
       </c>
       <c r="B151" s="4">
@@ -14132,7 +14105,7 @@
       </c>
     </row>
     <row r="152" ht="16.5" spans="1:20">
-      <c r="A152" s="47">
+      <c r="A152" s="4">
         <v>10</v>
       </c>
       <c r="B152" s="4">
@@ -14147,11 +14120,11 @@
         <v>0.013125</v>
       </c>
       <c r="E152" s="8">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F152" s="14">
         <f t="shared" si="1"/>
-        <v>0.984375</v>
+        <v>0.065625</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>1</v>
@@ -14197,7 +14170,7 @@
       </c>
     </row>
     <row r="153" ht="16.5" spans="1:20">
-      <c r="A153" s="47">
+      <c r="A153" s="4">
         <v>9</v>
       </c>
       <c r="B153" s="4">
@@ -14212,11 +14185,11 @@
         <v>0.00140625</v>
       </c>
       <c r="E153" s="8">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F153" s="14">
         <f t="shared" si="1"/>
-        <v>0.00703125</v>
+        <v>0.0703125</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>1</v>
@@ -14262,7 +14235,7 @@
       </c>
     </row>
     <row r="154" ht="16.5" spans="1:20">
-      <c r="A154" s="47">
+      <c r="A154" s="4">
         <v>9</v>
       </c>
       <c r="B154" s="4">
@@ -14327,7 +14300,7 @@
       </c>
     </row>
     <row r="155" ht="16.5" spans="1:20">
-      <c r="A155" s="47">
+      <c r="A155" s="4">
         <v>9</v>
       </c>
       <c r="B155" s="4">
@@ -14342,11 +14315,11 @@
         <v>0.0140625</v>
       </c>
       <c r="E155" s="8">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F155" s="14">
         <f t="shared" si="1"/>
-        <v>0.703125</v>
+        <v>0.0703125</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>1</v>
@@ -14393,7 +14366,7 @@
     </row>
     <row r="156" ht="16.5" spans="1:20">
       <c r="A156" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>1</v>
@@ -14409,7 +14382,7 @@
       </c>
       <c r="F156" s="15">
         <f>SUM(F141:F155)</f>
-        <v>4.45880625</v>
+        <v>1.0452703125</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>1</v>
@@ -14516,9 +14489,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" customHeight="1" spans="1:20">
+    <row r="158" ht="14" customHeight="1" spans="1:20">
       <c r="A158" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>1</v>
@@ -14578,24 +14551,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="1:20">
+    <row r="159" ht="14" customHeight="1" spans="1:20">
       <c r="A159" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C159" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="D159" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C159" s="5" t="s">
+      <c r="E159" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D159" s="5" t="s">
+      <c r="F159" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="E159" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G159" s="6" t="s">
         <v>1</v>
@@ -14656,11 +14629,11 @@
         <v>0.0003125</v>
       </c>
       <c r="E160" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F160" s="14">
         <f t="shared" ref="F160:F174" si="3">D160*E160</f>
-        <v>0.0015625</v>
+        <v>0.03125</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>1</v>
@@ -14786,11 +14759,11 @@
         <v>0.0046875</v>
       </c>
       <c r="E162" s="8">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F162" s="14">
         <f t="shared" si="3"/>
-        <v>0.46875</v>
+        <v>0.0234375</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>1</v>
@@ -14851,11 +14824,11 @@
         <v>0.0003</v>
       </c>
       <c r="E163" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F163" s="14">
         <f t="shared" si="3"/>
-        <v>0.0015</v>
+        <v>0.03</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>1</v>
@@ -14981,11 +14954,11 @@
         <v>0.0048</v>
       </c>
       <c r="E165" s="8">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F165" s="14">
         <f t="shared" si="3"/>
-        <v>0.48</v>
+        <v>0.024</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>1</v>
@@ -15046,11 +15019,11 @@
         <v>0.001125</v>
       </c>
       <c r="E166" s="8">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F166" s="14">
         <f t="shared" si="3"/>
-        <v>0.005625</v>
+        <v>0.084375</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>1</v>
@@ -15176,11 +15149,11 @@
         <v>0.01125</v>
       </c>
       <c r="E168" s="8">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F168" s="14">
         <f t="shared" si="3"/>
-        <v>0.84375</v>
+        <v>0.05625</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>1</v>
@@ -15226,7 +15199,7 @@
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:20">
-      <c r="A169" s="47">
+      <c r="A169" s="4">
         <v>10</v>
       </c>
       <c r="B169" s="4">
@@ -15241,11 +15214,11 @@
         <v>0.0009375</v>
       </c>
       <c r="E169" s="8">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F169" s="14">
         <f t="shared" si="3"/>
-        <v>0.0046875</v>
+        <v>0.0703125</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>1</v>
@@ -15291,7 +15264,7 @@
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:20">
-      <c r="A170" s="47">
+      <c r="A170" s="4">
         <v>10</v>
       </c>
       <c r="B170" s="4">
@@ -15356,7 +15329,7 @@
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:20">
-      <c r="A171" s="47">
+      <c r="A171" s="4">
         <v>10</v>
       </c>
       <c r="B171" s="4">
@@ -15371,11 +15344,11 @@
         <v>0.009375</v>
       </c>
       <c r="E171" s="8">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F171" s="14">
         <f t="shared" si="3"/>
-        <v>0.703125</v>
+        <v>0.046875</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>1</v>
@@ -15421,7 +15394,7 @@
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:20">
-      <c r="A172" s="47">
+      <c r="A172" s="4">
         <v>9</v>
       </c>
       <c r="B172" s="4">
@@ -15436,11 +15409,11 @@
         <v>0.001640625</v>
       </c>
       <c r="E172" s="8">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F172" s="14">
         <f t="shared" si="3"/>
-        <v>0.008203125</v>
+        <v>0.08203125</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>1</v>
@@ -15486,7 +15459,7 @@
       </c>
     </row>
     <row r="173" ht="16.5" spans="1:20">
-      <c r="A173" s="47">
+      <c r="A173" s="4">
         <v>9</v>
       </c>
       <c r="B173" s="4">
@@ -15551,7 +15524,7 @@
       </c>
     </row>
     <row r="174" ht="16.5" spans="1:20">
-      <c r="A174" s="47">
+      <c r="A174" s="4">
         <v>9</v>
       </c>
       <c r="B174" s="4">
@@ -15566,11 +15539,11 @@
         <v>0.0140625</v>
       </c>
       <c r="E174" s="8">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F174" s="14">
         <f t="shared" si="3"/>
-        <v>0.703125</v>
+        <v>0.0703125</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>1</v>
@@ -15617,7 +15590,7 @@
     </row>
     <row r="175" ht="16.5" spans="1:20">
       <c r="A175" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>1</v>
@@ -15633,7 +15606,7 @@
       </c>
       <c r="F175" s="15">
         <f>SUM(F160:F174)</f>
-        <v>3.407046875</v>
+        <v>0.7055625</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>1</v>
@@ -15740,9 +15713,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" customHeight="1" spans="1:20">
+    <row r="177" ht="14" customHeight="1" spans="1:20">
       <c r="A177" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>1</v>
@@ -15802,24 +15775,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" customHeight="1" spans="1:20">
+    <row r="178" ht="14" customHeight="1" spans="1:20">
       <c r="A178" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C178" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B178" s="5" t="s">
+      <c r="D178" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C178" s="5" t="s">
+      <c r="E178" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D178" s="5" t="s">
+      <c r="F178" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G178" s="6" t="s">
         <v>1</v>
@@ -15880,11 +15853,11 @@
         <v>0.0003125</v>
       </c>
       <c r="E179" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F179" s="14">
         <f t="shared" ref="F179:F193" si="5">D179*E179</f>
-        <v>0.0015625</v>
+        <v>0.03125</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>1</v>
@@ -16010,11 +15983,11 @@
         <v>0.0046875</v>
       </c>
       <c r="E181" s="8">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F181" s="14">
         <f t="shared" si="5"/>
-        <v>0.46875</v>
+        <v>0.0234375</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>1</v>
@@ -16075,11 +16048,11 @@
         <v>0.00046875</v>
       </c>
       <c r="E182" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F182" s="14">
         <f t="shared" si="5"/>
-        <v>0.00234375</v>
+        <v>0.046875</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>1</v>
@@ -16205,11 +16178,11 @@
         <v>0.005625</v>
       </c>
       <c r="E184" s="8">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F184" s="14">
         <f t="shared" si="5"/>
-        <v>0.5625</v>
+        <v>0.028125</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>1</v>
@@ -16270,11 +16243,11 @@
         <v>0.001575</v>
       </c>
       <c r="E185" s="8">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F185" s="14">
         <f t="shared" si="5"/>
-        <v>0.007875</v>
+        <v>0.118125</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>1</v>
@@ -16400,11 +16373,11 @@
         <v>0.01225</v>
       </c>
       <c r="E187" s="8">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F187" s="14">
         <f t="shared" si="5"/>
-        <v>0.91875</v>
+        <v>0.06125</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>1</v>
@@ -16450,7 +16423,7 @@
       </c>
     </row>
     <row r="188" ht="16.5" spans="1:20">
-      <c r="A188" s="47">
+      <c r="A188" s="4">
         <v>10</v>
       </c>
       <c r="B188" s="4">
@@ -16465,11 +16438,11 @@
         <v>0.00140625</v>
       </c>
       <c r="E188" s="8">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F188" s="14">
         <f t="shared" si="5"/>
-        <v>0.00703125</v>
+        <v>0.10546875</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>1</v>
@@ -16515,7 +16488,7 @@
       </c>
     </row>
     <row r="189" ht="16.5" spans="1:20">
-      <c r="A189" s="47">
+      <c r="A189" s="4">
         <v>10</v>
       </c>
       <c r="B189" s="4">
@@ -16580,7 +16553,7 @@
       </c>
     </row>
     <row r="190" ht="16.5" spans="1:20">
-      <c r="A190" s="47">
+      <c r="A190" s="4">
         <v>10</v>
       </c>
       <c r="B190" s="4">
@@ -16595,11 +16568,11 @@
         <v>0.0109375</v>
       </c>
       <c r="E190" s="8">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F190" s="14">
         <f t="shared" si="5"/>
-        <v>0.8203125</v>
+        <v>0.0546875</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>1</v>
@@ -16645,7 +16618,7 @@
       </c>
     </row>
     <row r="191" ht="16.5" spans="1:20">
-      <c r="A191" s="47">
+      <c r="A191" s="4">
         <v>9</v>
       </c>
       <c r="B191" s="4">
@@ -16660,11 +16633,11 @@
         <v>0.0023625</v>
       </c>
       <c r="E191" s="8">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F191" s="14">
         <f t="shared" si="5"/>
-        <v>0.0118125</v>
+        <v>0.118125</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>1</v>
@@ -16710,7 +16683,7 @@
       </c>
     </row>
     <row r="192" ht="16.5" spans="1:20">
-      <c r="A192" s="47">
+      <c r="A192" s="4">
         <v>9</v>
       </c>
       <c r="B192" s="4">
@@ -16775,7 +16748,7 @@
       </c>
     </row>
     <row r="193" ht="16.5" spans="1:20">
-      <c r="A193" s="47">
+      <c r="A193" s="4">
         <v>9</v>
       </c>
       <c r="B193" s="4">
@@ -16790,11 +16763,11 @@
         <v>0.01575</v>
       </c>
       <c r="E193" s="8">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F193" s="14">
         <f t="shared" si="5"/>
-        <v>0.7875</v>
+        <v>0.07875</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>1</v>
@@ -16841,7 +16814,7 @@
     </row>
     <row r="194" ht="16.5" spans="1:20">
       <c r="A194" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>1</v>
@@ -16857,7 +16830,7 @@
       </c>
       <c r="F194" s="15">
         <f>SUM(F179:F193)</f>
-        <v>3.84409375</v>
+        <v>0.92175</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>1</v>
@@ -16964,9 +16937,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" customHeight="1" spans="1:20">
+    <row r="196" ht="14" customHeight="1" spans="1:20">
       <c r="A196" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>1</v>
@@ -17028,7 +17001,7 @@
     </row>
     <row r="197" ht="16.5" spans="1:20">
       <c r="A197" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>1</v>
@@ -17150,13 +17123,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" customHeight="1" spans="1:20">
+    <row r="199" ht="14" customHeight="1" spans="1:20">
       <c r="A199" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B199" s="16">
         <f>F156</f>
-        <v>4.45880625</v>
+        <v>1.0452703125</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>1</v>
@@ -17215,11 +17188,11 @@
     </row>
     <row r="200" ht="16.5" spans="1:20">
       <c r="A200" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B200" s="14">
         <f>F175</f>
-        <v>3.407046875</v>
+        <v>0.7055625</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>1</v>
@@ -17278,11 +17251,11 @@
     </row>
     <row r="201" ht="16.5" spans="1:20">
       <c r="A201" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B201" s="14">
         <f>F194</f>
-        <v>3.84409375</v>
+        <v>0.92175</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>1</v>
@@ -17403,11 +17376,11 @@
     </row>
     <row r="203" ht="16.5" spans="1:20">
       <c r="A203" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B203" s="15">
         <f>AVERAGE(B199:B201)</f>
-        <v>3.903315625</v>
+        <v>0.8908609375</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>1</v>
@@ -17528,7 +17501,7 @@
     </row>
     <row r="205" ht="16.5" spans="1:20">
       <c r="A205" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B205" s="17">
         <v>0.7056</v>
@@ -17599,7 +17572,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Y225" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:Y140 A141:D155 F141:Y155 A156:Y159 A160:D160 F160:Y160 A161:Y161 A162:D163 F162:Y163 A164:Y164 A165:D166 F165:Y166 A167:Y167 A168:D169 F168:Y169 A170:Y170 A171:D172 F171:Y172 A173:Y173 A174:D174 F174:Y174 A175:Y178 A179:D193 F179:Y193 A194:Y225" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/游戏设计王/老虎机数学专题-中列扩展百搭.xlsx
+++ b/游戏设计王/老虎机数学专题-中列扩展百搭.xlsx
@@ -512,12 +512,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1229,7 +1230,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1296,6 +1297,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -13400,14 +13408,14 @@
         <f>B45*B65*B85*B105*B125</f>
         <v>2160</v>
       </c>
-      <c r="D141" s="13">
+      <c r="D141" s="36">
         <f t="shared" ref="D141:D155" si="0">C141/3200000</f>
         <v>0.000675</v>
       </c>
       <c r="E141" s="8">
         <v>100</v>
       </c>
-      <c r="F141" s="14">
+      <c r="F141" s="37">
         <f t="shared" ref="F141:F155" si="1">D141*E141</f>
         <v>0.0675</v>
       </c>
@@ -13465,14 +13473,14 @@
         <f>B45*B65*B85*B105*B130</f>
         <v>6480</v>
       </c>
-      <c r="D142" s="13">
+      <c r="D142" s="36">
         <f t="shared" si="0"/>
         <v>0.002025</v>
       </c>
       <c r="E142" s="8">
         <v>30</v>
       </c>
-      <c r="F142" s="14">
+      <c r="F142" s="37">
         <f t="shared" si="1"/>
         <v>0.06075</v>
       </c>
@@ -13530,14 +13538,14 @@
         <f>B45*B65*B85*B110*20</f>
         <v>20160</v>
       </c>
-      <c r="D143" s="13">
+      <c r="D143" s="36">
         <f t="shared" si="0"/>
         <v>0.0063</v>
       </c>
       <c r="E143" s="8">
         <v>5</v>
       </c>
-      <c r="F143" s="14">
+      <c r="F143" s="37">
         <f t="shared" si="1"/>
         <v>0.0315</v>
       </c>
@@ -13595,14 +13603,14 @@
         <f>B46*B66*B86*B106*B126</f>
         <v>1875</v>
       </c>
-      <c r="D144" s="13">
+      <c r="D144" s="36">
         <f t="shared" si="0"/>
         <v>0.0005859375</v>
       </c>
       <c r="E144" s="8">
         <v>100</v>
       </c>
-      <c r="F144" s="14">
+      <c r="F144" s="37">
         <f t="shared" si="1"/>
         <v>0.05859375</v>
       </c>
@@ -13660,14 +13668,14 @@
         <f>B46*B66*B86*B106*B131</f>
         <v>5625</v>
       </c>
-      <c r="D145" s="13">
+      <c r="D145" s="36">
         <f t="shared" si="0"/>
         <v>0.0017578125</v>
       </c>
       <c r="E145" s="8">
         <v>25</v>
       </c>
-      <c r="F145" s="14">
+      <c r="F145" s="37">
         <f t="shared" si="1"/>
         <v>0.0439453125</v>
       </c>
@@ -13725,14 +13733,14 @@
         <f>B46*B66*B86*B111*20</f>
         <v>22500</v>
       </c>
-      <c r="D146" s="13">
+      <c r="D146" s="36">
         <f t="shared" si="0"/>
         <v>0.00703125</v>
       </c>
       <c r="E146" s="8">
         <v>5</v>
       </c>
-      <c r="F146" s="14">
+      <c r="F146" s="37">
         <f t="shared" si="1"/>
         <v>0.03515625</v>
       </c>
@@ -13790,14 +13798,14 @@
         <f>B47*B67*B87*B107*B127</f>
         <v>6048</v>
       </c>
-      <c r="D147" s="13">
+      <c r="D147" s="36">
         <f t="shared" si="0"/>
         <v>0.00189</v>
       </c>
       <c r="E147" s="8">
         <v>75</v>
       </c>
-      <c r="F147" s="14">
+      <c r="F147" s="37">
         <f t="shared" si="1"/>
         <v>0.14175</v>
       </c>
@@ -13855,14 +13863,14 @@
         <f>B47*B67*B87*B107*B132</f>
         <v>14112</v>
       </c>
-      <c r="D148" s="13">
+      <c r="D148" s="36">
         <f t="shared" si="0"/>
         <v>0.00441</v>
       </c>
       <c r="E148" s="8">
         <v>20</v>
       </c>
-      <c r="F148" s="14">
+      <c r="F148" s="37">
         <f t="shared" si="1"/>
         <v>0.0882</v>
       </c>
@@ -13920,14 +13928,14 @@
         <f>B47*B67*B87*B112*20</f>
         <v>47040</v>
       </c>
-      <c r="D149" s="13">
+      <c r="D149" s="36">
         <f t="shared" si="0"/>
         <v>0.0147</v>
       </c>
       <c r="E149" s="8">
         <v>5</v>
       </c>
-      <c r="F149" s="14">
+      <c r="F149" s="37">
         <f t="shared" si="1"/>
         <v>0.0735</v>
       </c>
@@ -13985,14 +13993,14 @@
         <f>B48*B68*B88*B108*B128</f>
         <v>5400</v>
       </c>
-      <c r="D150" s="13">
+      <c r="D150" s="36">
         <f t="shared" si="0"/>
         <v>0.0016875</v>
       </c>
       <c r="E150" s="8">
         <v>75</v>
       </c>
-      <c r="F150" s="14">
+      <c r="F150" s="37">
         <f t="shared" si="1"/>
         <v>0.1265625</v>
       </c>
@@ -14050,14 +14058,14 @@
         <f>B48*B68*B88*B108*B133</f>
         <v>12600</v>
       </c>
-      <c r="D151" s="13">
+      <c r="D151" s="36">
         <f t="shared" si="0"/>
         <v>0.0039375</v>
       </c>
       <c r="E151" s="8">
         <v>20</v>
       </c>
-      <c r="F151" s="14">
+      <c r="F151" s="37">
         <f t="shared" si="1"/>
         <v>0.07875</v>
       </c>
@@ -14115,14 +14123,14 @@
         <f>B48*B68*B88*B113*20</f>
         <v>42000</v>
       </c>
-      <c r="D152" s="13">
+      <c r="D152" s="36">
         <f t="shared" si="0"/>
         <v>0.013125</v>
       </c>
       <c r="E152" s="8">
         <v>5</v>
       </c>
-      <c r="F152" s="14">
+      <c r="F152" s="37">
         <f t="shared" si="1"/>
         <v>0.065625</v>
       </c>
@@ -14180,14 +14188,14 @@
         <f>B49*B69*B89*B109*B129</f>
         <v>4500</v>
       </c>
-      <c r="D153" s="13">
+      <c r="D153" s="36">
         <f t="shared" si="0"/>
         <v>0.00140625</v>
       </c>
       <c r="E153" s="8">
         <v>50</v>
       </c>
-      <c r="F153" s="14">
+      <c r="F153" s="37">
         <f t="shared" si="1"/>
         <v>0.0703125</v>
       </c>
@@ -14245,14 +14253,14 @@
         <f>B49*B69*B89*B109*B134</f>
         <v>10500</v>
       </c>
-      <c r="D154" s="13">
+      <c r="D154" s="36">
         <f t="shared" si="0"/>
         <v>0.00328125</v>
       </c>
       <c r="E154" s="8">
         <v>10</v>
       </c>
-      <c r="F154" s="14">
+      <c r="F154" s="37">
         <f t="shared" si="1"/>
         <v>0.0328125</v>
       </c>
@@ -14310,14 +14318,14 @@
         <f>B49*B69*B89*B114*20</f>
         <v>45000</v>
       </c>
-      <c r="D155" s="13">
+      <c r="D155" s="36">
         <f t="shared" si="0"/>
         <v>0.0140625</v>
       </c>
       <c r="E155" s="8">
         <v>5</v>
       </c>
-      <c r="F155" s="14">
+      <c r="F155" s="37">
         <f t="shared" si="1"/>
         <v>0.0703125</v>
       </c>
@@ -14380,7 +14388,7 @@
       <c r="E156" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F156" s="15">
+      <c r="F156" s="38">
         <f>SUM(F141:F155)</f>
         <v>1.0452703125</v>
       </c>
@@ -14624,14 +14632,14 @@
         <f>B45*K65*K85*K105*T125</f>
         <v>1000</v>
       </c>
-      <c r="D160" s="13">
+      <c r="D160" s="36">
         <f t="shared" ref="D160:D174" si="2">C160/3200000</f>
         <v>0.0003125</v>
       </c>
       <c r="E160" s="8">
         <v>100</v>
       </c>
-      <c r="F160" s="14">
+      <c r="F160" s="37">
         <f t="shared" ref="F160:F174" si="3">D160*E160</f>
         <v>0.03125</v>
       </c>
@@ -14689,14 +14697,14 @@
         <f>B45*K65*K85*K105*T130</f>
         <v>4000</v>
       </c>
-      <c r="D161" s="13">
+      <c r="D161" s="36">
         <f t="shared" si="2"/>
         <v>0.00125</v>
       </c>
       <c r="E161" s="8">
         <v>30</v>
       </c>
-      <c r="F161" s="14">
+      <c r="F161" s="37">
         <f t="shared" si="3"/>
         <v>0.0375</v>
       </c>
@@ -14754,14 +14762,14 @@
         <f>B45*K65*K85*K110*20</f>
         <v>15000</v>
       </c>
-      <c r="D162" s="13">
+      <c r="D162" s="36">
         <f t="shared" si="2"/>
         <v>0.0046875</v>
       </c>
       <c r="E162" s="8">
         <v>5</v>
       </c>
-      <c r="F162" s="14">
+      <c r="F162" s="37">
         <f t="shared" si="3"/>
         <v>0.0234375</v>
       </c>
@@ -14819,14 +14827,14 @@
         <f>B46*K66*K86*K106*T126</f>
         <v>960</v>
       </c>
-      <c r="D163" s="13">
+      <c r="D163" s="36">
         <f t="shared" si="2"/>
         <v>0.0003</v>
       </c>
       <c r="E163" s="8">
         <v>100</v>
       </c>
-      <c r="F163" s="14">
+      <c r="F163" s="37">
         <f t="shared" si="3"/>
         <v>0.03</v>
       </c>
@@ -14884,14 +14892,14 @@
         <f>B46*K66*K86*K106*T131</f>
         <v>2880</v>
       </c>
-      <c r="D164" s="13">
+      <c r="D164" s="36">
         <f t="shared" si="2"/>
         <v>0.0009</v>
       </c>
       <c r="E164" s="8">
         <v>25</v>
       </c>
-      <c r="F164" s="14">
+      <c r="F164" s="37">
         <f t="shared" si="3"/>
         <v>0.0225</v>
       </c>
@@ -14949,14 +14957,14 @@
         <f>B46*K66*K86*K111*20</f>
         <v>15360</v>
       </c>
-      <c r="D165" s="13">
+      <c r="D165" s="36">
         <f t="shared" si="2"/>
         <v>0.0048</v>
       </c>
       <c r="E165" s="8">
         <v>5</v>
       </c>
-      <c r="F165" s="14">
+      <c r="F165" s="37">
         <f t="shared" si="3"/>
         <v>0.024</v>
       </c>
@@ -15014,14 +15022,14 @@
         <f>B47*K67*K87*K107*T127</f>
         <v>3600</v>
       </c>
-      <c r="D166" s="13">
+      <c r="D166" s="36">
         <f t="shared" si="2"/>
         <v>0.001125</v>
       </c>
       <c r="E166" s="8">
         <v>75</v>
       </c>
-      <c r="F166" s="14">
+      <c r="F166" s="37">
         <f t="shared" si="3"/>
         <v>0.084375</v>
       </c>
@@ -15079,14 +15087,14 @@
         <f>B47*K67*K87*K107*T132</f>
         <v>8400</v>
       </c>
-      <c r="D167" s="13">
+      <c r="D167" s="36">
         <f t="shared" si="2"/>
         <v>0.002625</v>
       </c>
       <c r="E167" s="8">
         <v>20</v>
       </c>
-      <c r="F167" s="14">
+      <c r="F167" s="37">
         <f t="shared" si="3"/>
         <v>0.0525</v>
       </c>
@@ -15144,14 +15152,14 @@
         <f>B47*K67*K87*K112*20</f>
         <v>36000</v>
       </c>
-      <c r="D168" s="13">
+      <c r="D168" s="36">
         <f t="shared" si="2"/>
         <v>0.01125</v>
       </c>
       <c r="E168" s="8">
         <v>5</v>
       </c>
-      <c r="F168" s="14">
+      <c r="F168" s="37">
         <f t="shared" si="3"/>
         <v>0.05625</v>
       </c>
@@ -15209,14 +15217,14 @@
         <f>B48*K68*K88*K108*T128</f>
         <v>3000</v>
       </c>
-      <c r="D169" s="13">
+      <c r="D169" s="36">
         <f t="shared" si="2"/>
         <v>0.0009375</v>
       </c>
       <c r="E169" s="8">
         <v>75</v>
       </c>
-      <c r="F169" s="14">
+      <c r="F169" s="37">
         <f t="shared" si="3"/>
         <v>0.0703125</v>
       </c>
@@ -15274,14 +15282,14 @@
         <f>B48*K68*K88*K108*T133</f>
         <v>7000</v>
       </c>
-      <c r="D170" s="13">
+      <c r="D170" s="36">
         <f t="shared" si="2"/>
         <v>0.0021875</v>
       </c>
       <c r="E170" s="8">
         <v>20</v>
       </c>
-      <c r="F170" s="14">
+      <c r="F170" s="37">
         <f t="shared" si="3"/>
         <v>0.04375</v>
       </c>
@@ -15339,14 +15347,14 @@
         <f>B48*K68*K88*K113*20</f>
         <v>30000</v>
       </c>
-      <c r="D171" s="13">
+      <c r="D171" s="36">
         <f t="shared" si="2"/>
         <v>0.009375</v>
       </c>
       <c r="E171" s="8">
         <v>5</v>
       </c>
-      <c r="F171" s="14">
+      <c r="F171" s="37">
         <f t="shared" si="3"/>
         <v>0.046875</v>
       </c>
@@ -15404,14 +15412,14 @@
         <f>B49*K69*K89*K109*T129</f>
         <v>5250</v>
       </c>
-      <c r="D172" s="13">
+      <c r="D172" s="36">
         <f t="shared" si="2"/>
         <v>0.001640625</v>
       </c>
       <c r="E172" s="8">
         <v>50</v>
       </c>
-      <c r="F172" s="14">
+      <c r="F172" s="37">
         <f t="shared" si="3"/>
         <v>0.08203125</v>
       </c>
@@ -15469,14 +15477,14 @@
         <f>B49*K69*K89*K109*T134</f>
         <v>9750</v>
       </c>
-      <c r="D173" s="13">
+      <c r="D173" s="36">
         <f t="shared" si="2"/>
         <v>0.003046875</v>
       </c>
       <c r="E173" s="8">
         <v>10</v>
       </c>
-      <c r="F173" s="14">
+      <c r="F173" s="37">
         <f t="shared" si="3"/>
         <v>0.03046875</v>
       </c>
@@ -15534,14 +15542,14 @@
         <f>B49*K69*K89*K114*20</f>
         <v>45000</v>
       </c>
-      <c r="D174" s="13">
+      <c r="D174" s="36">
         <f t="shared" si="2"/>
         <v>0.0140625</v>
       </c>
       <c r="E174" s="8">
         <v>5</v>
       </c>
-      <c r="F174" s="14">
+      <c r="F174" s="37">
         <f t="shared" si="3"/>
         <v>0.0703125</v>
       </c>
@@ -15604,7 +15612,7 @@
       <c r="E175" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F175" s="15">
+      <c r="F175" s="38">
         <f>SUM(F160:F174)</f>
         <v>0.7055625</v>
       </c>
@@ -15848,14 +15856,14 @@
         <f>B45*T65*K85*T105*T125</f>
         <v>1000</v>
       </c>
-      <c r="D179" s="13">
+      <c r="D179" s="36">
         <f t="shared" ref="D179:D193" si="4">C179/3200000</f>
         <v>0.0003125</v>
       </c>
       <c r="E179" s="8">
         <v>100</v>
       </c>
-      <c r="F179" s="14">
+      <c r="F179" s="37">
         <f t="shared" ref="F179:F193" si="5">D179*E179</f>
         <v>0.03125</v>
       </c>
@@ -15913,14 +15921,14 @@
         <f>B45*T65*K85*T105*T130</f>
         <v>4000</v>
       </c>
-      <c r="D180" s="13">
+      <c r="D180" s="36">
         <f t="shared" si="4"/>
         <v>0.00125</v>
       </c>
       <c r="E180" s="8">
         <v>30</v>
       </c>
-      <c r="F180" s="14">
+      <c r="F180" s="37">
         <f t="shared" si="5"/>
         <v>0.0375</v>
       </c>
@@ -15978,14 +15986,14 @@
         <f>B45*T65*K85*T110*20</f>
         <v>15000</v>
       </c>
-      <c r="D181" s="13">
+      <c r="D181" s="36">
         <f t="shared" si="4"/>
         <v>0.0046875</v>
       </c>
       <c r="E181" s="8">
         <v>5</v>
       </c>
-      <c r="F181" s="14">
+      <c r="F181" s="37">
         <f t="shared" si="5"/>
         <v>0.0234375</v>
       </c>
@@ -16043,14 +16051,14 @@
         <f>B46*T66*K86*T106*T126</f>
         <v>1500</v>
       </c>
-      <c r="D182" s="13">
+      <c r="D182" s="36">
         <f t="shared" si="4"/>
         <v>0.00046875</v>
       </c>
       <c r="E182" s="8">
         <v>100</v>
       </c>
-      <c r="F182" s="14">
+      <c r="F182" s="37">
         <f t="shared" si="5"/>
         <v>0.046875</v>
       </c>
@@ -16108,14 +16116,14 @@
         <f>B46*T66*K86*T106*T131</f>
         <v>4500</v>
       </c>
-      <c r="D183" s="13">
+      <c r="D183" s="36">
         <f t="shared" si="4"/>
         <v>0.00140625</v>
       </c>
       <c r="E183" s="8">
         <v>25</v>
       </c>
-      <c r="F183" s="14">
+      <c r="F183" s="37">
         <f t="shared" si="5"/>
         <v>0.03515625</v>
       </c>
@@ -16173,14 +16181,14 @@
         <f>B46*T66*K86*T111*20</f>
         <v>18000</v>
       </c>
-      <c r="D184" s="13">
+      <c r="D184" s="36">
         <f t="shared" si="4"/>
         <v>0.005625</v>
       </c>
       <c r="E184" s="8">
         <v>5</v>
       </c>
-      <c r="F184" s="14">
+      <c r="F184" s="37">
         <f t="shared" si="5"/>
         <v>0.028125</v>
       </c>
@@ -16238,14 +16246,14 @@
         <f>B47*T67*K87*T107*T127</f>
         <v>5040</v>
       </c>
-      <c r="D185" s="13">
+      <c r="D185" s="36">
         <f t="shared" si="4"/>
         <v>0.001575</v>
       </c>
       <c r="E185" s="8">
         <v>75</v>
       </c>
-      <c r="F185" s="14">
+      <c r="F185" s="37">
         <f t="shared" si="5"/>
         <v>0.118125</v>
       </c>
@@ -16303,14 +16311,14 @@
         <f>B47*T67*K87*T107*T132</f>
         <v>11760</v>
       </c>
-      <c r="D186" s="13">
+      <c r="D186" s="36">
         <f t="shared" si="4"/>
         <v>0.003675</v>
       </c>
       <c r="E186" s="8">
         <v>20</v>
       </c>
-      <c r="F186" s="14">
+      <c r="F186" s="37">
         <f t="shared" si="5"/>
         <v>0.0735</v>
       </c>
@@ -16368,14 +16376,14 @@
         <f>B47*T67*K87*T112*20</f>
         <v>39200</v>
       </c>
-      <c r="D187" s="13">
+      <c r="D187" s="36">
         <f t="shared" si="4"/>
         <v>0.01225</v>
       </c>
       <c r="E187" s="8">
         <v>5</v>
       </c>
-      <c r="F187" s="14">
+      <c r="F187" s="37">
         <f t="shared" si="5"/>
         <v>0.06125</v>
       </c>
@@ -16433,14 +16441,14 @@
         <f>B48*T68*K88*T108*T128</f>
         <v>4500</v>
       </c>
-      <c r="D188" s="13">
+      <c r="D188" s="36">
         <f t="shared" si="4"/>
         <v>0.00140625</v>
       </c>
       <c r="E188" s="8">
         <v>75</v>
       </c>
-      <c r="F188" s="14">
+      <c r="F188" s="37">
         <f t="shared" si="5"/>
         <v>0.10546875</v>
       </c>
@@ -16498,14 +16506,14 @@
         <f>B48*T68*K88*T108*T133</f>
         <v>10500</v>
       </c>
-      <c r="D189" s="13">
+      <c r="D189" s="36">
         <f t="shared" si="4"/>
         <v>0.00328125</v>
       </c>
       <c r="E189" s="8">
         <v>20</v>
       </c>
-      <c r="F189" s="14">
+      <c r="F189" s="37">
         <f t="shared" si="5"/>
         <v>0.065625</v>
       </c>
@@ -16563,14 +16571,14 @@
         <f>B48*T68*K88*T113*20</f>
         <v>35000</v>
       </c>
-      <c r="D190" s="13">
+      <c r="D190" s="36">
         <f t="shared" si="4"/>
         <v>0.0109375</v>
       </c>
       <c r="E190" s="8">
         <v>5</v>
       </c>
-      <c r="F190" s="14">
+      <c r="F190" s="37">
         <f t="shared" si="5"/>
         <v>0.0546875</v>
       </c>
@@ -16628,14 +16636,14 @@
         <f>B49*T69*K89*T109*T129</f>
         <v>7560</v>
       </c>
-      <c r="D191" s="13">
+      <c r="D191" s="36">
         <f t="shared" si="4"/>
         <v>0.0023625</v>
       </c>
       <c r="E191" s="8">
         <v>50</v>
       </c>
-      <c r="F191" s="14">
+      <c r="F191" s="37">
         <f t="shared" si="5"/>
         <v>0.118125</v>
       </c>
@@ -16693,14 +16701,14 @@
         <f>B49*T69*K89*T109*T134</f>
         <v>14040</v>
       </c>
-      <c r="D192" s="13">
+      <c r="D192" s="36">
         <f t="shared" si="4"/>
         <v>0.0043875</v>
       </c>
       <c r="E192" s="8">
         <v>10</v>
       </c>
-      <c r="F192" s="14">
+      <c r="F192" s="37">
         <f t="shared" si="5"/>
         <v>0.043875</v>
       </c>
@@ -16758,14 +16766,14 @@
         <f>B49*T69*K89*T114*20</f>
         <v>50400</v>
       </c>
-      <c r="D193" s="13">
+      <c r="D193" s="36">
         <f t="shared" si="4"/>
         <v>0.01575</v>
       </c>
       <c r="E193" s="8">
         <v>5</v>
       </c>
-      <c r="F193" s="14">
+      <c r="F193" s="37">
         <f t="shared" si="5"/>
         <v>0.07875</v>
       </c>
@@ -16828,7 +16836,7 @@
       <c r="E194" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F194" s="15">
+      <c r="F194" s="38">
         <f>SUM(F179:F193)</f>
         <v>0.92175</v>
       </c>
@@ -17127,7 +17135,7 @@
       <c r="A199" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B199" s="16">
+      <c r="B199" s="39">
         <f>F156</f>
         <v>1.0452703125</v>
       </c>
@@ -17190,7 +17198,7 @@
       <c r="A200" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B200" s="14">
+      <c r="B200" s="37">
         <f>F175</f>
         <v>0.7055625</v>
       </c>
@@ -17253,7 +17261,7 @@
       <c r="A201" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B201" s="14">
+      <c r="B201" s="37">
         <f>F194</f>
         <v>0.92175</v>
       </c>
@@ -17378,7 +17386,7 @@
       <c r="A203" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B203" s="15">
+      <c r="B203" s="38">
         <f>AVERAGE(B199:B201)</f>
         <v>0.8908609375</v>
       </c>
